--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -31,8 +31,8 @@
     <sheet name="Central" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Outer Burlington" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="Central South" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Route 15" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Route 7" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Route 7" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Route 15" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="Warren - Waitsfield" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="Route 2 East" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="Southern Ski Slopes" sheetId="29" state="visible" r:id="rId29"/>
@@ -54189,7 +54189,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>1800</v>
+        <v>1815</v>
       </c>
       <c r="S142" t="n">
         <v>20</v>
@@ -54324,7 +54324,7 @@
         <v>0</v>
       </c>
       <c r="BK142" t="n">
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="BL142" t="n">
         <v>0</v>
@@ -54378,7 +54378,7 @@
         <v>0</v>
       </c>
       <c r="CC142" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CD142" t="n">
         <v>134</v>
@@ -54462,7 +54462,7 @@
         <v>0</v>
       </c>
       <c r="DE142" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="DF142" t="n">
         <v>415</v>
@@ -54510,7 +54510,7 @@
         <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>9239</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="143">
@@ -54568,7 +54568,7 @@
         <v>105</v>
       </c>
       <c r="R143" t="n">
-        <v>440111</v>
+        <v>440126</v>
       </c>
       <c r="S143" t="n">
         <v>995</v>
@@ -54703,7 +54703,7 @@
         <v>660</v>
       </c>
       <c r="BK143" t="n">
-        <v>48586</v>
+        <v>49035</v>
       </c>
       <c r="BL143" t="n">
         <v>1992</v>
@@ -54757,7 +54757,7 @@
         <v>435</v>
       </c>
       <c r="CC143" t="n">
-        <v>16350</v>
+        <v>16375</v>
       </c>
       <c r="CD143" t="n">
         <v>6042</v>
@@ -54841,7 +54841,7 @@
         <v>90</v>
       </c>
       <c r="DE143" t="n">
-        <v>21351</v>
+        <v>21646</v>
       </c>
       <c r="DF143" t="n">
         <v>39089</v>
@@ -54889,7 +54889,7 @@
         <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2129345</v>
+        <v>2130129</v>
       </c>
     </row>
   </sheetData>
@@ -54944,12 +54944,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -55013,10 +55013,10 @@
         <v>120</v>
       </c>
       <c r="H2" t="n">
+        <v>185</v>
+      </c>
+      <c r="I2" t="n">
         <v>690</v>
-      </c>
-      <c r="I2" t="n">
-        <v>185</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -55065,10 +55065,10 @@
         <v>665</v>
       </c>
       <c r="H3" t="n">
+        <v>365</v>
+      </c>
+      <c r="I3" t="n">
         <v>72</v>
-      </c>
-      <c r="I3" t="n">
-        <v>365</v>
       </c>
       <c r="J3" t="n">
         <v>450</v>
@@ -55117,10 +55117,10 @@
         <v>420</v>
       </c>
       <c r="H4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I4" t="n">
         <v>695</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1200</v>
       </c>
       <c r="J4" t="n">
         <v>190</v>
@@ -55169,10 +55169,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
+        <v>650</v>
+      </c>
+      <c r="I5" t="n">
         <v>563</v>
-      </c>
-      <c r="I5" t="n">
-        <v>650</v>
       </c>
       <c r="J5" t="n">
         <v>410</v>
@@ -55221,10 +55221,10 @@
         <v>495</v>
       </c>
       <c r="H6" t="n">
+        <v>810</v>
+      </c>
+      <c r="I6" t="n">
         <v>475</v>
-      </c>
-      <c r="I6" t="n">
-        <v>810</v>
       </c>
       <c r="J6" t="n">
         <v>245</v>
@@ -55273,10 +55273,10 @@
         <v>645</v>
       </c>
       <c r="H7" t="n">
+        <v>615</v>
+      </c>
+      <c r="I7" t="n">
         <v>480</v>
-      </c>
-      <c r="I7" t="n">
-        <v>615</v>
       </c>
       <c r="J7" t="n">
         <v>150</v>
@@ -55325,10 +55325,10 @@
         <v>410</v>
       </c>
       <c r="H8" t="n">
+        <v>545</v>
+      </c>
+      <c r="I8" t="n">
         <v>584</v>
-      </c>
-      <c r="I8" t="n">
-        <v>545</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -55377,10 +55377,10 @@
         <v>785</v>
       </c>
       <c r="H9" t="n">
+        <v>605</v>
+      </c>
+      <c r="I9" t="n">
         <v>347</v>
-      </c>
-      <c r="I9" t="n">
-        <v>605</v>
       </c>
       <c r="J9" t="n">
         <v>330</v>
@@ -55429,10 +55429,10 @@
         <v>700</v>
       </c>
       <c r="H10" t="n">
+        <v>990</v>
+      </c>
+      <c r="I10" t="n">
         <v>70</v>
-      </c>
-      <c r="I10" t="n">
-        <v>990</v>
       </c>
       <c r="J10" t="n">
         <v>590</v>
@@ -55481,10 +55481,10 @@
         <v>760</v>
       </c>
       <c r="H11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I11" t="n">
         <v>606</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1050</v>
       </c>
       <c r="J11" t="n">
         <v>140</v>
@@ -55533,10 +55533,10 @@
         <v>580</v>
       </c>
       <c r="H12" t="n">
+        <v>655</v>
+      </c>
+      <c r="I12" t="n">
         <v>335</v>
-      </c>
-      <c r="I12" t="n">
-        <v>655</v>
       </c>
       <c r="J12" t="n">
         <v>250</v>
@@ -55585,10 +55585,10 @@
         <v>590</v>
       </c>
       <c r="H13" t="n">
+        <v>905</v>
+      </c>
+      <c r="I13" t="n">
         <v>570</v>
-      </c>
-      <c r="I13" t="n">
-        <v>905</v>
       </c>
       <c r="J13" t="n">
         <v>130</v>
@@ -55637,10 +55637,10 @@
         <v>6570</v>
       </c>
       <c r="H14" t="n">
+        <v>8575</v>
+      </c>
+      <c r="I14" t="n">
         <v>5487</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8575</v>
       </c>
       <c r="J14" t="n">
         <v>2985</v>
@@ -55716,12 +55716,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -55785,10 +55785,10 @@
         <v>430</v>
       </c>
       <c r="H2" t="n">
+        <v>550</v>
+      </c>
+      <c r="I2" t="n">
         <v>358</v>
-      </c>
-      <c r="I2" t="n">
-        <v>550</v>
       </c>
       <c r="J2" t="n">
         <v>485</v>
@@ -55837,10 +55837,10 @@
         <v>520</v>
       </c>
       <c r="H3" t="n">
+        <v>905</v>
+      </c>
+      <c r="I3" t="n">
         <v>254</v>
-      </c>
-      <c r="I3" t="n">
-        <v>905</v>
       </c>
       <c r="J3" t="n">
         <v>240</v>
@@ -55889,10 +55889,10 @@
         <v>410</v>
       </c>
       <c r="H4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I4" t="n">
         <v>680</v>
-      </c>
-      <c r="I4" t="n">
-        <v>690</v>
       </c>
       <c r="J4" t="n">
         <v>300</v>
@@ -55941,10 +55941,10 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
+        <v>1335</v>
+      </c>
+      <c r="I5" t="n">
         <v>1000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1335</v>
       </c>
       <c r="J5" t="n">
         <v>575</v>
@@ -55993,10 +55993,10 @@
         <v>555</v>
       </c>
       <c r="H6" t="n">
+        <v>375</v>
+      </c>
+      <c r="I6" t="n">
         <v>175</v>
-      </c>
-      <c r="I6" t="n">
-        <v>375</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -56045,10 +56045,10 @@
         <v>950</v>
       </c>
       <c r="H7" t="n">
+        <v>1070</v>
+      </c>
+      <c r="I7" t="n">
         <v>1160</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1070</v>
       </c>
       <c r="J7" t="n">
         <v>450</v>
@@ -56097,10 +56097,10 @@
         <v>880</v>
       </c>
       <c r="H8" t="n">
+        <v>995</v>
+      </c>
+      <c r="I8" t="n">
         <v>340</v>
-      </c>
-      <c r="I8" t="n">
-        <v>995</v>
       </c>
       <c r="J8" t="n">
         <v>205</v>
@@ -56149,10 +56149,10 @@
         <v>540</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="I9" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>670</v>
@@ -56201,10 +56201,10 @@
         <v>680</v>
       </c>
       <c r="H10" t="n">
+        <v>935</v>
+      </c>
+      <c r="I10" t="n">
         <v>1180</v>
-      </c>
-      <c r="I10" t="n">
-        <v>935</v>
       </c>
       <c r="J10" t="n">
         <v>320</v>
@@ -56253,10 +56253,10 @@
         <v>790</v>
       </c>
       <c r="H11" t="n">
+        <v>675</v>
+      </c>
+      <c r="I11" t="n">
         <v>1025</v>
-      </c>
-      <c r="I11" t="n">
-        <v>675</v>
       </c>
       <c r="J11" t="n">
         <v>470</v>
@@ -56305,10 +56305,10 @@
         <v>400</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="I12" t="n">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>815</v>
@@ -56357,10 +56357,10 @@
         <v>680</v>
       </c>
       <c r="H13" t="n">
+        <v>400</v>
+      </c>
+      <c r="I13" t="n">
         <v>740</v>
-      </c>
-      <c r="I13" t="n">
-        <v>400</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -56409,10 +56409,10 @@
         <v>7475</v>
       </c>
       <c r="H14" t="n">
+        <v>9305</v>
+      </c>
+      <c r="I14" t="n">
         <v>6912</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9305</v>
       </c>
       <c r="J14" t="n">
         <v>4530</v>
@@ -56488,12 +56488,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -56557,10 +56557,10 @@
         <v>390</v>
       </c>
       <c r="H2" t="n">
+        <v>1375</v>
+      </c>
+      <c r="I2" t="n">
         <v>715</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1375</v>
       </c>
       <c r="J2" t="n">
         <v>675</v>
@@ -56609,10 +56609,10 @@
         <v>725</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>315</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>950</v>
@@ -56661,10 +56661,10 @@
         <v>700</v>
       </c>
       <c r="H4" t="n">
+        <v>945</v>
+      </c>
+      <c r="I4" t="n">
         <v>850</v>
-      </c>
-      <c r="I4" t="n">
-        <v>945</v>
       </c>
       <c r="J4" t="n">
         <v>1270</v>
@@ -56713,10 +56713,10 @@
         <v>250</v>
       </c>
       <c r="H5" t="n">
+        <v>1020</v>
+      </c>
+      <c r="I5" t="n">
         <v>850</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1020</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -56765,10 +56765,10 @@
         <v>245</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="I6" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>150</v>
@@ -56817,10 +56817,10 @@
         <v>275</v>
       </c>
       <c r="H7" t="n">
+        <v>855</v>
+      </c>
+      <c r="I7" t="n">
         <v>1020</v>
-      </c>
-      <c r="I7" t="n">
-        <v>855</v>
       </c>
       <c r="J7" t="n">
         <v>455</v>
@@ -56869,10 +56869,10 @@
         <v>575</v>
       </c>
       <c r="H8" t="n">
+        <v>1155</v>
+      </c>
+      <c r="I8" t="n">
         <v>900</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1155</v>
       </c>
       <c r="J8" t="n">
         <v>290</v>
@@ -56921,10 +56921,10 @@
         <v>725</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="I9" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>275</v>
@@ -56973,10 +56973,10 @@
         <v>795</v>
       </c>
       <c r="H10" t="n">
+        <v>750</v>
+      </c>
+      <c r="I10" t="n">
         <v>400</v>
-      </c>
-      <c r="I10" t="n">
-        <v>750</v>
       </c>
       <c r="J10" t="n">
         <v>80</v>
@@ -57025,10 +57025,10 @@
         <v>485</v>
       </c>
       <c r="H11" t="n">
+        <v>855</v>
+      </c>
+      <c r="I11" t="n">
         <v>885</v>
-      </c>
-      <c r="I11" t="n">
-        <v>855</v>
       </c>
       <c r="J11" t="n">
         <v>525</v>
@@ -57077,10 +57077,10 @@
         <v>920</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>920</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>360</v>
@@ -57129,10 +57129,10 @@
         <v>305</v>
       </c>
       <c r="H13" t="n">
+        <v>1085</v>
+      </c>
+      <c r="I13" t="n">
         <v>1145</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1085</v>
       </c>
       <c r="J13" t="n">
         <v>395</v>
@@ -57181,10 +57181,10 @@
         <v>6390</v>
       </c>
       <c r="H14" t="n">
+        <v>8935</v>
+      </c>
+      <c r="I14" t="n">
         <v>8000</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8935</v>
       </c>
       <c r="J14" t="n">
         <v>5425</v>
@@ -57260,12 +57260,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -57329,10 +57329,10 @@
         <v>440</v>
       </c>
       <c r="H2" t="n">
+        <v>445</v>
+      </c>
+      <c r="I2" t="n">
         <v>475</v>
-      </c>
-      <c r="I2" t="n">
-        <v>445</v>
       </c>
       <c r="J2" t="n">
         <v>295</v>
@@ -57381,10 +57381,10 @@
         <v>350</v>
       </c>
       <c r="H3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I3" t="n">
         <v>810</v>
-      </c>
-      <c r="I3" t="n">
-        <v>75</v>
       </c>
       <c r="J3" t="n">
         <v>680</v>
@@ -57433,10 +57433,10 @@
         <v>225</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="I4" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>740</v>
@@ -57485,10 +57485,10 @@
         <v>325</v>
       </c>
       <c r="H5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I5" t="n">
         <v>775</v>
-      </c>
-      <c r="I5" t="n">
-        <v>150</v>
       </c>
       <c r="J5" t="n">
         <v>900</v>
@@ -57537,10 +57537,10 @@
         <v>1175</v>
       </c>
       <c r="H6" t="n">
+        <v>925</v>
+      </c>
+      <c r="I6" t="n">
         <v>1060</v>
-      </c>
-      <c r="I6" t="n">
-        <v>925</v>
       </c>
       <c r="J6" t="n">
         <v>440</v>
@@ -57589,10 +57589,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>310</v>
+      </c>
+      <c r="I7" t="n">
         <v>1030</v>
-      </c>
-      <c r="I7" t="n">
-        <v>310</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -57693,10 +57693,10 @@
         <v>875</v>
       </c>
       <c r="H9" t="n">
+        <v>585</v>
+      </c>
+      <c r="I9" t="n">
         <v>230</v>
-      </c>
-      <c r="I9" t="n">
-        <v>585</v>
       </c>
       <c r="J9" t="n">
         <v>655</v>
@@ -57745,10 +57745,10 @@
         <v>680</v>
       </c>
       <c r="H10" t="n">
+        <v>780</v>
+      </c>
+      <c r="I10" t="n">
         <v>225</v>
-      </c>
-      <c r="I10" t="n">
-        <v>780</v>
       </c>
       <c r="J10" t="n">
         <v>675</v>
@@ -57797,10 +57797,10 @@
         <v>850</v>
       </c>
       <c r="H11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="I11" t="n">
         <v>465</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1125</v>
       </c>
       <c r="J11" t="n">
         <v>610</v>
@@ -57849,10 +57849,10 @@
         <v>260</v>
       </c>
       <c r="H12" t="n">
+        <v>360</v>
+      </c>
+      <c r="I12" t="n">
         <v>635</v>
-      </c>
-      <c r="I12" t="n">
-        <v>360</v>
       </c>
       <c r="J12" t="n">
         <v>445</v>
@@ -57901,10 +57901,10 @@
         <v>680</v>
       </c>
       <c r="H13" t="n">
+        <v>850</v>
+      </c>
+      <c r="I13" t="n">
         <v>455</v>
-      </c>
-      <c r="I13" t="n">
-        <v>850</v>
       </c>
       <c r="J13" t="n">
         <v>380</v>
@@ -57953,10 +57953,10 @@
         <v>6760</v>
       </c>
       <c r="H14" t="n">
+        <v>7145</v>
+      </c>
+      <c r="I14" t="n">
         <v>7080</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7145</v>
       </c>
       <c r="J14" t="n">
         <v>6245</v>
@@ -58032,12 +58032,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -58101,10 +58101,10 @@
         <v>185</v>
       </c>
       <c r="H2" t="n">
+        <v>520</v>
+      </c>
+      <c r="I2" t="n">
         <v>615</v>
-      </c>
-      <c r="I2" t="n">
-        <v>520</v>
       </c>
       <c r="J2" t="n">
         <v>440</v>
@@ -58153,10 +58153,10 @@
         <v>470</v>
       </c>
       <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
         <v>845</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>320</v>
@@ -58205,10 +58205,10 @@
         <v>350</v>
       </c>
       <c r="H4" t="n">
+        <v>807</v>
+      </c>
+      <c r="I4" t="n">
         <v>945</v>
-      </c>
-      <c r="I4" t="n">
-        <v>807</v>
       </c>
       <c r="J4" t="n">
         <v>830</v>
@@ -58257,10 +58257,10 @@
         <v>305</v>
       </c>
       <c r="H5" t="n">
+        <v>740</v>
+      </c>
+      <c r="I5" t="n">
         <v>1090</v>
-      </c>
-      <c r="I5" t="n">
-        <v>740</v>
       </c>
       <c r="J5" t="n">
         <v>1090</v>
@@ -58309,10 +58309,10 @@
         <v>665</v>
       </c>
       <c r="H6" t="n">
+        <v>465</v>
+      </c>
+      <c r="I6" t="n">
         <v>255</v>
-      </c>
-      <c r="I6" t="n">
-        <v>465</v>
       </c>
       <c r="J6" t="n">
         <v>500</v>
@@ -58361,10 +58361,10 @@
         <v>1085</v>
       </c>
       <c r="H7" t="n">
+        <v>1095</v>
+      </c>
+      <c r="I7" t="n">
         <v>1130</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1095</v>
       </c>
       <c r="J7" t="n">
         <v>550</v>
@@ -58413,10 +58413,10 @@
         <v>1080</v>
       </c>
       <c r="H8" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I8" t="n">
         <v>405</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1005</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -58465,10 +58465,10 @@
         <v>880</v>
       </c>
       <c r="H9" t="n">
+        <v>1295</v>
+      </c>
+      <c r="I9" t="n">
         <v>1230</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1295</v>
       </c>
       <c r="J9" t="n">
         <v>665</v>
@@ -58517,10 +58517,10 @@
         <v>1507</v>
       </c>
       <c r="H10" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I10" t="n">
         <v>1294</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1044</v>
       </c>
       <c r="J10" t="n">
         <v>615</v>
@@ -58569,10 +58569,10 @@
         <v>1386</v>
       </c>
       <c r="H11" t="n">
+        <v>430</v>
+      </c>
+      <c r="I11" t="n">
         <v>760</v>
-      </c>
-      <c r="I11" t="n">
-        <v>430</v>
       </c>
       <c r="J11" t="n">
         <v>675</v>
@@ -58621,10 +58621,10 @@
         <v>709</v>
       </c>
       <c r="H12" t="n">
+        <v>1446</v>
+      </c>
+      <c r="I12" t="n">
         <v>2740</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1446</v>
       </c>
       <c r="J12" t="n">
         <v>325</v>
@@ -58673,10 +58673,10 @@
         <v>212</v>
       </c>
       <c r="H13" t="n">
+        <v>508</v>
+      </c>
+      <c r="I13" t="n">
         <v>635</v>
-      </c>
-      <c r="I13" t="n">
-        <v>508</v>
       </c>
       <c r="J13" t="n">
         <v>20</v>
@@ -58725,10 +58725,10 @@
         <v>8834</v>
       </c>
       <c r="H14" t="n">
+        <v>9375</v>
+      </c>
+      <c r="I14" t="n">
         <v>11944</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9375</v>
       </c>
       <c r="J14" t="n">
         <v>6030</v>
@@ -58804,12 +58804,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -58873,10 +58873,10 @@
         <v>685</v>
       </c>
       <c r="H2" t="n">
+        <v>599</v>
+      </c>
+      <c r="I2" t="n">
         <v>275</v>
-      </c>
-      <c r="I2" t="n">
-        <v>599</v>
       </c>
       <c r="J2" t="n">
         <v>730</v>
@@ -58925,10 +58925,10 @@
         <v>180</v>
       </c>
       <c r="H3" t="n">
+        <v>730</v>
+      </c>
+      <c r="I3" t="n">
         <v>1045</v>
-      </c>
-      <c r="I3" t="n">
-        <v>730</v>
       </c>
       <c r="J3" t="n">
         <v>650</v>
@@ -58977,10 +58977,10 @@
         <v>518</v>
       </c>
       <c r="H4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="I4" t="n">
         <v>655</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1357</v>
       </c>
       <c r="J4" t="n">
         <v>1375</v>
@@ -59029,10 +59029,10 @@
         <v>607</v>
       </c>
       <c r="H5" t="n">
+        <v>679</v>
+      </c>
+      <c r="I5" t="n">
         <v>839</v>
-      </c>
-      <c r="I5" t="n">
-        <v>679</v>
       </c>
       <c r="J5" t="n">
         <v>615</v>
@@ -59081,10 +59081,10 @@
         <v>1036</v>
       </c>
       <c r="H6" t="n">
+        <v>790</v>
+      </c>
+      <c r="I6" t="n">
         <v>1108</v>
-      </c>
-      <c r="I6" t="n">
-        <v>790</v>
       </c>
       <c r="J6" t="n">
         <v>380</v>
@@ -59133,10 +59133,10 @@
         <v>1121</v>
       </c>
       <c r="H7" t="n">
+        <v>683</v>
+      </c>
+      <c r="I7" t="n">
         <v>981</v>
-      </c>
-      <c r="I7" t="n">
-        <v>683</v>
       </c>
       <c r="J7" t="n">
         <v>465</v>
@@ -59185,10 +59185,10 @@
         <v>622</v>
       </c>
       <c r="H8" t="n">
+        <v>850</v>
+      </c>
+      <c r="I8" t="n">
         <v>365</v>
-      </c>
-      <c r="I8" t="n">
-        <v>850</v>
       </c>
       <c r="J8" t="n">
         <v>870</v>
@@ -59237,10 +59237,10 @@
         <v>1225</v>
       </c>
       <c r="H9" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I9" t="n">
         <v>797</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2032</v>
       </c>
       <c r="J9" t="n">
         <v>880</v>
@@ -59289,10 +59289,10 @@
         <v>934</v>
       </c>
       <c r="H10" t="n">
+        <v>545</v>
+      </c>
+      <c r="I10" t="n">
         <v>930</v>
-      </c>
-      <c r="I10" t="n">
-        <v>545</v>
       </c>
       <c r="J10" t="n">
         <v>147</v>
@@ -59341,10 +59341,10 @@
         <v>1776</v>
       </c>
       <c r="H11" t="n">
+        <v>595</v>
+      </c>
+      <c r="I11" t="n">
         <v>2036</v>
-      </c>
-      <c r="I11" t="n">
-        <v>595</v>
       </c>
       <c r="J11" t="n">
         <v>688</v>
@@ -59393,10 +59393,10 @@
         <v>725</v>
       </c>
       <c r="H12" t="n">
+        <v>979</v>
+      </c>
+      <c r="I12" t="n">
         <v>930</v>
-      </c>
-      <c r="I12" t="n">
-        <v>979</v>
       </c>
       <c r="J12" t="n">
         <v>325</v>
@@ -59445,10 +59445,10 @@
         <v>480</v>
       </c>
       <c r="H13" t="n">
+        <v>847</v>
+      </c>
+      <c r="I13" t="n">
         <v>1162</v>
-      </c>
-      <c r="I13" t="n">
-        <v>847</v>
       </c>
       <c r="J13" t="n">
         <v>455</v>
@@ -59497,10 +59497,10 @@
         <v>9909</v>
       </c>
       <c r="H14" t="n">
+        <v>10686</v>
+      </c>
+      <c r="I14" t="n">
         <v>11123</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10686</v>
       </c>
       <c r="J14" t="n">
         <v>7580</v>
@@ -59576,12 +59576,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -59645,10 +59645,10 @@
         <v>605</v>
       </c>
       <c r="H2" t="n">
+        <v>872</v>
+      </c>
+      <c r="I2" t="n">
         <v>927</v>
-      </c>
-      <c r="I2" t="n">
-        <v>872</v>
       </c>
       <c r="J2" t="n">
         <v>1070</v>
@@ -59697,10 +59697,10 @@
         <v>954</v>
       </c>
       <c r="H3" t="n">
+        <v>630</v>
+      </c>
+      <c r="I3" t="n">
         <v>950</v>
-      </c>
-      <c r="I3" t="n">
-        <v>630</v>
       </c>
       <c r="J3" t="n">
         <v>1319</v>
@@ -59749,10 +59749,10 @@
         <v>619</v>
       </c>
       <c r="H4" t="n">
+        <v>699</v>
+      </c>
+      <c r="I4" t="n">
         <v>360</v>
-      </c>
-      <c r="I4" t="n">
-        <v>699</v>
       </c>
       <c r="J4" t="n">
         <v>725</v>
@@ -59801,10 +59801,10 @@
         <v>1077</v>
       </c>
       <c r="H5" t="n">
+        <v>1040</v>
+      </c>
+      <c r="I5" t="n">
         <v>1180</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1040</v>
       </c>
       <c r="J5" t="n">
         <v>1025</v>
@@ -59853,10 +59853,10 @@
         <v>1005</v>
       </c>
       <c r="H6" t="n">
+        <v>632</v>
+      </c>
+      <c r="I6" t="n">
         <v>185</v>
-      </c>
-      <c r="I6" t="n">
-        <v>632</v>
       </c>
       <c r="J6" t="n">
         <v>180</v>
@@ -59905,10 +59905,10 @@
         <v>1879</v>
       </c>
       <c r="H7" t="n">
+        <v>805</v>
+      </c>
+      <c r="I7" t="n">
         <v>1261</v>
-      </c>
-      <c r="I7" t="n">
-        <v>805</v>
       </c>
       <c r="J7" t="n">
         <v>1085</v>
@@ -59957,10 +59957,10 @@
         <v>905</v>
       </c>
       <c r="H8" t="n">
+        <v>3466</v>
+      </c>
+      <c r="I8" t="n">
         <v>1690</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3466</v>
       </c>
       <c r="J8" t="n">
         <v>740</v>
@@ -60009,10 +60009,10 @@
         <v>1514</v>
       </c>
       <c r="H9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="I9" t="n">
         <v>425</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1202</v>
       </c>
       <c r="J9" t="n">
         <v>560</v>
@@ -60061,10 +60061,10 @@
         <v>1240</v>
       </c>
       <c r="H10" t="n">
+        <v>775</v>
+      </c>
+      <c r="I10" t="n">
         <v>1165</v>
-      </c>
-      <c r="I10" t="n">
-        <v>775</v>
       </c>
       <c r="J10" t="n">
         <v>670</v>
@@ -60113,10 +60113,10 @@
         <v>1373</v>
       </c>
       <c r="H11" t="n">
+        <v>640</v>
+      </c>
+      <c r="I11" t="n">
         <v>821</v>
-      </c>
-      <c r="I11" t="n">
-        <v>640</v>
       </c>
       <c r="J11" t="n">
         <v>555</v>
@@ -60165,10 +60165,10 @@
         <v>1022</v>
       </c>
       <c r="H12" t="n">
+        <v>642</v>
+      </c>
+      <c r="I12" t="n">
         <v>1935</v>
-      </c>
-      <c r="I12" t="n">
-        <v>642</v>
       </c>
       <c r="J12" t="n">
         <v>530</v>
@@ -60217,10 +60217,10 @@
         <v>524</v>
       </c>
       <c r="H13" t="n">
+        <v>992</v>
+      </c>
+      <c r="I13" t="n">
         <v>1064</v>
-      </c>
-      <c r="I13" t="n">
-        <v>992</v>
       </c>
       <c r="J13" t="n">
         <v>145</v>
@@ -60269,10 +60269,10 @@
         <v>12717</v>
       </c>
       <c r="H14" t="n">
+        <v>12395</v>
+      </c>
+      <c r="I14" t="n">
         <v>11963</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12395</v>
       </c>
       <c r="J14" t="n">
         <v>8604</v>
@@ -60348,12 +60348,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -60417,10 +60417,10 @@
         <v>473</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="I2" t="n">
-        <v>903</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1395</v>
@@ -60469,10 +60469,10 @@
         <v>552</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1314</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>360</v>
@@ -60521,10 +60521,10 @@
         <v>899</v>
       </c>
       <c r="H4" t="n">
+        <v>630</v>
+      </c>
+      <c r="I4" t="n">
         <v>215</v>
-      </c>
-      <c r="I4" t="n">
-        <v>630</v>
       </c>
       <c r="J4" t="n">
         <v>1770</v>
@@ -60573,10 +60573,10 @@
         <v>510</v>
       </c>
       <c r="H5" t="n">
+        <v>1537</v>
+      </c>
+      <c r="I5" t="n">
         <v>1723</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1537</v>
       </c>
       <c r="J5" t="n">
         <v>975</v>
@@ -60625,10 +60625,10 @@
         <v>1010</v>
       </c>
       <c r="H6" t="n">
+        <v>1486</v>
+      </c>
+      <c r="I6" t="n">
         <v>999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1486</v>
       </c>
       <c r="J6" t="n">
         <v>660</v>
@@ -60677,10 +60677,10 @@
         <v>1342</v>
       </c>
       <c r="H7" t="n">
+        <v>1430</v>
+      </c>
+      <c r="I7" t="n">
         <v>645</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1430</v>
       </c>
       <c r="J7" t="n">
         <v>470</v>
@@ -60729,10 +60729,10 @@
         <v>2162</v>
       </c>
       <c r="H8" t="n">
+        <v>708</v>
+      </c>
+      <c r="I8" t="n">
         <v>1101</v>
-      </c>
-      <c r="I8" t="n">
-        <v>708</v>
       </c>
       <c r="J8" t="n">
         <v>600</v>
@@ -60781,10 +60781,10 @@
         <v>1615</v>
       </c>
       <c r="H9" t="n">
+        <v>1341</v>
+      </c>
+      <c r="I9" t="n">
         <v>975</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1341</v>
       </c>
       <c r="J9" t="n">
         <v>1120</v>
@@ -60833,10 +60833,10 @@
         <v>1482</v>
       </c>
       <c r="H10" t="n">
+        <v>1296</v>
+      </c>
+      <c r="I10" t="n">
         <v>1120</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1296</v>
       </c>
       <c r="J10" t="n">
         <v>450</v>
@@ -60885,10 +60885,10 @@
         <v>1467</v>
       </c>
       <c r="H11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="I11" t="n">
         <v>1420</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1103</v>
       </c>
       <c r="J11" t="n">
         <v>296</v>
@@ -60937,10 +60937,10 @@
         <v>914</v>
       </c>
       <c r="H12" t="n">
+        <v>770</v>
+      </c>
+      <c r="I12" t="n">
         <v>1185</v>
-      </c>
-      <c r="I12" t="n">
-        <v>770</v>
       </c>
       <c r="J12" t="n">
         <v>685</v>
@@ -60989,10 +60989,10 @@
         <v>777</v>
       </c>
       <c r="H13" t="n">
+        <v>948</v>
+      </c>
+      <c r="I13" t="n">
         <v>90</v>
-      </c>
-      <c r="I13" t="n">
-        <v>948</v>
       </c>
       <c r="J13" t="n">
         <v>820</v>
@@ -61041,10 +61041,10 @@
         <v>13203</v>
       </c>
       <c r="H14" t="n">
+        <v>12152</v>
+      </c>
+      <c r="I14" t="n">
         <v>10787</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12152</v>
       </c>
       <c r="J14" t="n">
         <v>9601</v>
@@ -61120,12 +61120,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -61189,10 +61189,10 @@
         <v>870</v>
       </c>
       <c r="H2" t="n">
+        <v>852</v>
+      </c>
+      <c r="I2" t="n">
         <v>945</v>
-      </c>
-      <c r="I2" t="n">
-        <v>852</v>
       </c>
       <c r="J2" t="n">
         <v>1185</v>
@@ -61241,10 +61241,10 @@
         <v>469</v>
       </c>
       <c r="H3" t="n">
+        <v>875</v>
+      </c>
+      <c r="I3" t="n">
         <v>815</v>
-      </c>
-      <c r="I3" t="n">
-        <v>875</v>
       </c>
       <c r="J3" t="n">
         <v>800</v>
@@ -61293,10 +61293,10 @@
         <v>1193</v>
       </c>
       <c r="H4" t="n">
+        <v>564</v>
+      </c>
+      <c r="I4" t="n">
         <v>1080</v>
-      </c>
-      <c r="I4" t="n">
-        <v>564</v>
       </c>
       <c r="J4" t="n">
         <v>1400</v>
@@ -61345,10 +61345,10 @@
         <v>1263</v>
       </c>
       <c r="H5" t="n">
+        <v>1490</v>
+      </c>
+      <c r="I5" t="n">
         <v>930</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1490</v>
       </c>
       <c r="J5" t="n">
         <v>370</v>
@@ -61397,10 +61397,10 @@
         <v>1280</v>
       </c>
       <c r="H6" t="n">
+        <v>1155</v>
+      </c>
+      <c r="I6" t="n">
         <v>1684</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1155</v>
       </c>
       <c r="J6" t="n">
         <v>820</v>
@@ -61449,10 +61449,10 @@
         <v>1979</v>
       </c>
       <c r="H7" t="n">
+        <v>590</v>
+      </c>
+      <c r="I7" t="n">
         <v>1475</v>
-      </c>
-      <c r="I7" t="n">
-        <v>590</v>
       </c>
       <c r="J7" t="n">
         <v>425</v>
@@ -61501,10 +61501,10 @@
         <v>1815</v>
       </c>
       <c r="H8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I8" t="n">
         <v>385</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2025</v>
       </c>
       <c r="J8" t="n">
         <v>965</v>
@@ -61553,10 +61553,10 @@
         <v>1176</v>
       </c>
       <c r="H9" t="n">
+        <v>925</v>
+      </c>
+      <c r="I9" t="n">
         <v>1745</v>
-      </c>
-      <c r="I9" t="n">
-        <v>925</v>
       </c>
       <c r="J9" t="n">
         <v>700</v>
@@ -61587,7 +61587,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1940</v>
+        <v>1955</v>
       </c>
       <c r="C10" t="n">
         <v>324</v>
@@ -61605,16 +61605,16 @@
         <v>1209</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I10" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>525</v>
       </c>
       <c r="K10" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -61629,7 +61629,7 @@
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8274</v>
+        <v>9058</v>
       </c>
     </row>
     <row r="11">
@@ -61639,7 +61639,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41532</v>
+        <v>41547</v>
       </c>
       <c r="C11" t="n">
         <v>28499</v>
@@ -61657,16 +61657,16 @@
         <v>11254</v>
       </c>
       <c r="H11" t="n">
+        <v>9365</v>
+      </c>
+      <c r="I11" t="n">
         <v>9059</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8621</v>
       </c>
       <c r="J11" t="n">
         <v>7190</v>
       </c>
       <c r="K11" t="n">
-        <v>6120</v>
+        <v>6145</v>
       </c>
       <c r="L11" t="n">
         <v>6055</v>
@@ -61681,7 +61681,7 @@
         <v>2730</v>
       </c>
       <c r="P11" t="n">
-        <v>195775</v>
+        <v>196559</v>
       </c>
     </row>
   </sheetData>
@@ -63117,7 +63117,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1940</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="143">
@@ -63127,7 +63127,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>506963</v>
+        <v>506978</v>
       </c>
     </row>
     <row r="145">
@@ -63235,7 +63235,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>41532</v>
+        <v>41547</v>
       </c>
     </row>
     <row r="158">
@@ -63245,7 +63245,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>506963</v>
+        <v>506978</v>
       </c>
     </row>
   </sheetData>
@@ -71906,7 +71906,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>145</v>
+        <v>889</v>
       </c>
       <c r="C142" t="n">
         <v>410</v>
@@ -71915,7 +71915,7 @@
         <v>325</v>
       </c>
       <c r="E142" t="n">
-        <v>4195</v>
+        <v>4210</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -71948,7 +71948,7 @@
         <v>95</v>
       </c>
       <c r="P142" t="n">
-        <v>1821</v>
+        <v>1846</v>
       </c>
       <c r="Q142" t="n">
         <v>105</v>
@@ -71957,7 +71957,7 @@
         <v>1040</v>
       </c>
       <c r="S142" t="n">
-        <v>9239</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="143">
@@ -71967,7 +71967,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>80002</v>
+        <v>80746</v>
       </c>
       <c r="C143" t="n">
         <v>18589</v>
@@ -71976,7 +71976,7 @@
         <v>64162</v>
       </c>
       <c r="E143" t="n">
-        <v>877734</v>
+        <v>877749</v>
       </c>
       <c r="F143" t="n">
         <v>6157</v>
@@ -72009,7 +72009,7 @@
         <v>24911</v>
       </c>
       <c r="P143" t="n">
-        <v>432426</v>
+        <v>432451</v>
       </c>
       <c r="Q143" t="n">
         <v>36889</v>
@@ -72018,7 +72018,7 @@
         <v>91600</v>
       </c>
       <c r="S143" t="n">
-        <v>2129345</v>
+        <v>2130129</v>
       </c>
     </row>
   </sheetData>
@@ -79584,17 +79584,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>345</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2015-03</t>
+          <t>2015-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>410</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -79604,7 +79604,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
@@ -79614,7 +79614,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
@@ -79624,163 +79624,163 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>375</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>335</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2015-11</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>297</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>170</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>335</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>285</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -79790,1121 +79790,1121 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>355</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>289</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>225</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>180</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>344</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2017-04</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>498</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>398</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>823</v>
+        <v>699</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>158</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>631</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>515</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>274</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>479</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>322</v>
+        <v>650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>690</v>
+        <v>810</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>72</v>
+        <v>615</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>695</v>
+        <v>545</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>563</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>475</v>
+        <v>990</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>584</v>
+        <v>655</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>347</v>
+        <v>905</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>70</v>
+        <v>550</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>606</v>
+        <v>905</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>335</v>
+        <v>690</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>570</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>254</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>680</v>
+        <v>995</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1000</v>
+        <v>615</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>175</v>
+        <v>935</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1160</v>
+        <v>675</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>340</v>
+        <v>760</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1180</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1025</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>740</v>
+        <v>945</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>715</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>315</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>850</v>
+        <v>855</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>850</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1020</v>
+        <v>770</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>400</v>
+        <v>855</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>885</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>920</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1145</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>475</v>
+        <v>620</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>810</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>775</v>
+        <v>925</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1060</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1030</v>
+        <v>920</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>920</v>
+        <v>585</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>230</v>
+        <v>780</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>225</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>465</v>
+        <v>360</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>635</v>
+        <v>850</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>455</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>615</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>845</v>
+        <v>807</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>945</v>
+        <v>740</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1090</v>
+        <v>465</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>255</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1130</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>405</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1230</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1294</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>760</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2740</v>
+        <v>508</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>635</v>
+        <v>599</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>275</v>
+        <v>730</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1045</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>655</v>
+        <v>679</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>839</v>
+        <v>790</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1108</v>
+        <v>683</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>981</v>
+        <v>850</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>365</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>797</v>
+        <v>545</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>930</v>
+        <v>595</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2036</v>
+        <v>979</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>930</v>
+        <v>847</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1162</v>
+        <v>872</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>927</v>
+        <v>630</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>950</v>
+        <v>699</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>360</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1180</v>
+        <v>632</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>185</v>
+        <v>805</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1261</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1690</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>425</v>
+        <v>775</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1165</v>
+        <v>640</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>821</v>
+        <v>642</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1935</v>
+        <v>992</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1064</v>
+        <v>903</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1314</v>
+        <v>630</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>215</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1723</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>999</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>645</v>
+        <v>708</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1101</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>975</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1120</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1420</v>
+        <v>770</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1185</v>
+        <v>948</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>90</v>
+        <v>852</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>945</v>
+        <v>875</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>815</v>
+        <v>564</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1080</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>930</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1684</v>
+        <v>590</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1475</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>385</v>
+        <v>925</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1745</v>
+        <v>889</v>
       </c>
     </row>
     <row r="135">
@@ -80914,7 +80914,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>93618</v>
+        <v>95427</v>
       </c>
     </row>
     <row r="137">
@@ -80934,7 +80934,7 @@
         <v>2015</v>
       </c>
       <c r="B138" t="n">
-        <v>2907</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="139">
@@ -80942,7 +80942,7 @@
         <v>2016</v>
       </c>
       <c r="B139" t="n">
-        <v>3509</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="140">
@@ -80950,7 +80950,7 @@
         <v>2017</v>
       </c>
       <c r="B140" t="n">
-        <v>4847</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="141">
@@ -80958,7 +80958,7 @@
         <v>2018</v>
       </c>
       <c r="B141" t="n">
-        <v>5487</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="142">
@@ -80966,7 +80966,7 @@
         <v>2019</v>
       </c>
       <c r="B142" t="n">
-        <v>6912</v>
+        <v>9305</v>
       </c>
     </row>
     <row r="143">
@@ -80974,7 +80974,7 @@
         <v>2020</v>
       </c>
       <c r="B143" t="n">
-        <v>8000</v>
+        <v>8935</v>
       </c>
     </row>
     <row r="144">
@@ -80982,7 +80982,7 @@
         <v>2021</v>
       </c>
       <c r="B144" t="n">
-        <v>7080</v>
+        <v>7145</v>
       </c>
     </row>
     <row r="145">
@@ -80990,7 +80990,7 @@
         <v>2022</v>
       </c>
       <c r="B145" t="n">
-        <v>11944</v>
+        <v>9375</v>
       </c>
     </row>
     <row r="146">
@@ -80998,7 +80998,7 @@
         <v>2023</v>
       </c>
       <c r="B146" t="n">
-        <v>11123</v>
+        <v>10686</v>
       </c>
     </row>
     <row r="147">
@@ -81006,7 +81006,7 @@
         <v>2024</v>
       </c>
       <c r="B147" t="n">
-        <v>11963</v>
+        <v>12395</v>
       </c>
     </row>
     <row r="148">
@@ -81014,7 +81014,7 @@
         <v>2025</v>
       </c>
       <c r="B148" t="n">
-        <v>10787</v>
+        <v>12152</v>
       </c>
     </row>
     <row r="149">
@@ -81022,7 +81022,7 @@
         <v>2026</v>
       </c>
       <c r="B149" t="n">
-        <v>9059</v>
+        <v>9365</v>
       </c>
     </row>
     <row r="150">
@@ -81032,7 +81032,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>93618</v>
+        <v>95427</v>
       </c>
     </row>
   </sheetData>
@@ -81068,17 +81068,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2015-02</t>
+          <t>2015-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4">
@@ -81088,7 +81088,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
@@ -81098,7 +81098,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -81108,163 +81108,163 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-11</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>580</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>300</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>120</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>305</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>310</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -81274,1121 +81274,1121 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>235</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>355</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>385</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>310</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>225</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>235</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>699</v>
+        <v>823</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>325</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>375</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>185</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>365</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1200</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>650</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>810</v>
+        <v>690</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>615</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>545</v>
+        <v>695</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>605</v>
+        <v>563</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>990</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1050</v>
+        <v>480</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>655</v>
+        <v>584</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>905</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>550</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>905</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>690</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1335</v>
+        <v>570</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>375</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1070</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>995</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>615</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>935</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>675</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>760</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>400</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1375</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>945</v>
+        <v>740</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1020</v>
+        <v>715</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>125</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1155</v>
+        <v>850</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>770</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>855</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1085</v>
+        <v>885</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>445</v>
+        <v>920</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>75</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>620</v>
+        <v>475</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>150</v>
+        <v>810</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>925</v>
+        <v>775</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>310</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>920</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>585</v>
+        <v>920</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>780</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1125</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>360</v>
+        <v>465</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>850</v>
+        <v>635</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>520</v>
+        <v>455</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>20</v>
+        <v>615</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>807</v>
+        <v>845</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>740</v>
+        <v>945</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>465</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1095</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1005</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1295</v>
+        <v>405</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1044</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>430</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1446</v>
+        <v>760</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>508</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>599</v>
+        <v>635</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>730</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1357</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>679</v>
+        <v>655</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>790</v>
+        <v>839</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>683</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>850</v>
+        <v>981</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2032</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>545</v>
+        <v>797</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>595</v>
+        <v>930</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>979</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>847</v>
+        <v>930</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>872</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>630</v>
+        <v>927</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>699</v>
+        <v>950</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1040</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>632</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>805</v>
+        <v>185</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3466</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1202</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>775</v>
+        <v>425</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>640</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>642</v>
+        <v>821</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>992</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>903</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>630</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1537</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1486</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1430</v>
+        <v>999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>708</v>
+        <v>645</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1341</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1296</v>
+        <v>975</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1103</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>770</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>948</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>852</v>
+        <v>90</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>875</v>
+        <v>945</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>564</v>
+        <v>815</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1490</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1155</v>
+        <v>930</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>590</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2025</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>925</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>145</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="135">
@@ -82398,7 +82398,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>94683</v>
+        <v>93618</v>
       </c>
     </row>
     <row r="137">
@@ -82418,7 +82418,7 @@
         <v>2015</v>
       </c>
       <c r="B138" t="n">
-        <v>1230</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="139">
@@ -82426,7 +82426,7 @@
         <v>2016</v>
       </c>
       <c r="B139" t="n">
-        <v>3040</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="140">
@@ -82434,7 +82434,7 @@
         <v>2017</v>
       </c>
       <c r="B140" t="n">
-        <v>3224</v>
+        <v>4847</v>
       </c>
     </row>
     <row r="141">
@@ -82442,7 +82442,7 @@
         <v>2018</v>
       </c>
       <c r="B141" t="n">
-        <v>8575</v>
+        <v>5487</v>
       </c>
     </row>
     <row r="142">
@@ -82450,7 +82450,7 @@
         <v>2019</v>
       </c>
       <c r="B142" t="n">
-        <v>9305</v>
+        <v>6912</v>
       </c>
     </row>
     <row r="143">
@@ -82458,7 +82458,7 @@
         <v>2020</v>
       </c>
       <c r="B143" t="n">
-        <v>8935</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="144">
@@ -82466,7 +82466,7 @@
         <v>2021</v>
       </c>
       <c r="B144" t="n">
-        <v>7145</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="145">
@@ -82474,7 +82474,7 @@
         <v>2022</v>
       </c>
       <c r="B145" t="n">
-        <v>9375</v>
+        <v>11944</v>
       </c>
     </row>
     <row r="146">
@@ -82482,7 +82482,7 @@
         <v>2023</v>
       </c>
       <c r="B146" t="n">
-        <v>10686</v>
+        <v>11123</v>
       </c>
     </row>
     <row r="147">
@@ -82490,7 +82490,7 @@
         <v>2024</v>
       </c>
       <c r="B147" t="n">
-        <v>12395</v>
+        <v>11963</v>
       </c>
     </row>
     <row r="148">
@@ -82498,7 +82498,7 @@
         <v>2025</v>
       </c>
       <c r="B148" t="n">
-        <v>12152</v>
+        <v>10787</v>
       </c>
     </row>
     <row r="149">
@@ -82506,7 +82506,7 @@
         <v>2026</v>
       </c>
       <c r="B149" t="n">
-        <v>8621</v>
+        <v>9059</v>
       </c>
     </row>
     <row r="150">
@@ -82516,7 +82516,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>94683</v>
+        <v>93618</v>
       </c>
     </row>
   </sheetData>
@@ -85236,7 +85236,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="127">
@@ -85246,7 +85246,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>46068</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="129">
@@ -85354,7 +85354,7 @@
         <v>2026</v>
       </c>
       <c r="B141" t="n">
-        <v>6120</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="142">
@@ -85364,7 +85364,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>46068</v>
+        <v>46093</v>
       </c>
     </row>
   </sheetData>
@@ -94299,7 +94299,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1940</v>
+        <v>1955</v>
       </c>
       <c r="C142" t="n">
         <v>1056</v>
@@ -94323,10 +94323,10 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="K142" t="n">
-        <v>145</v>
+        <v>889</v>
       </c>
       <c r="L142" t="n">
         <v>455</v>
@@ -94344,7 +94344,7 @@
         <v>80</v>
       </c>
       <c r="Q142" t="n">
-        <v>9249</v>
+        <v>10033</v>
       </c>
     </row>
     <row r="143">
@@ -94354,7 +94354,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>506963</v>
+        <v>506978</v>
       </c>
       <c r="C143" t="n">
         <v>230634</v>
@@ -94378,10 +94378,10 @@
         <v>93618</v>
       </c>
       <c r="J143" t="n">
-        <v>46068</v>
+        <v>46093</v>
       </c>
       <c r="K143" t="n">
-        <v>94683</v>
+        <v>95427</v>
       </c>
       <c r="L143" t="n">
         <v>25543</v>
@@ -94399,7 +94399,7 @@
         <v>325674</v>
       </c>
       <c r="Q143" t="n">
-        <v>2162290</v>
+        <v>2163074</v>
       </c>
     </row>
   </sheetData>
@@ -102425,7 +102425,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>35400</v>
+        <v>35415</v>
       </c>
       <c r="S13" t="n">
         <v>210</v>
@@ -102560,7 +102560,7 @@
         <v>40</v>
       </c>
       <c r="BK13" t="n">
-        <v>3786</v>
+        <v>4235</v>
       </c>
       <c r="BL13" t="n">
         <v>0</v>
@@ -102614,7 +102614,7 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>2620</v>
+        <v>2645</v>
       </c>
       <c r="CD13" t="n">
         <v>1129</v>
@@ -102698,7 +102698,7 @@
         <v>90</v>
       </c>
       <c r="DE13" t="n">
-        <v>1840</v>
+        <v>2135</v>
       </c>
       <c r="DF13" t="n">
         <v>4415</v>
@@ -102746,7 +102746,7 @@
         <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>210578</v>
+        <v>211362</v>
       </c>
     </row>
     <row r="14">
@@ -102804,7 +102804,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>440111</v>
+        <v>440126</v>
       </c>
       <c r="S14" t="n">
         <v>995</v>
@@ -102939,7 +102939,7 @@
         <v>660</v>
       </c>
       <c r="BK14" t="n">
-        <v>48586</v>
+        <v>49035</v>
       </c>
       <c r="BL14" t="n">
         <v>1992</v>
@@ -102993,7 +102993,7 @@
         <v>435</v>
       </c>
       <c r="CC14" t="n">
-        <v>16350</v>
+        <v>16375</v>
       </c>
       <c r="CD14" t="n">
         <v>6042</v>
@@ -103077,7 +103077,7 @@
         <v>90</v>
       </c>
       <c r="DE14" t="n">
-        <v>21351</v>
+        <v>21646</v>
       </c>
       <c r="DF14" t="n">
         <v>39089</v>
@@ -103125,7 +103125,7 @@
         <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2129345</v>
+        <v>2130129</v>
       </c>
     </row>
   </sheetData>
@@ -103893,7 +103893,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>6961</v>
+        <v>7705</v>
       </c>
       <c r="C13" t="n">
         <v>3335</v>
@@ -103902,7 +103902,7 @@
         <v>6850</v>
       </c>
       <c r="E13" t="n">
-        <v>86909</v>
+        <v>86924</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -103935,7 +103935,7 @@
         <v>505</v>
       </c>
       <c r="P13" t="n">
-        <v>37977</v>
+        <v>38002</v>
       </c>
       <c r="Q13" t="n">
         <v>3485</v>
@@ -103944,7 +103944,7 @@
         <v>12267</v>
       </c>
       <c r="S13" t="n">
-        <v>210578</v>
+        <v>211362</v>
       </c>
     </row>
     <row r="14">
@@ -103954,7 +103954,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80002</v>
+        <v>80746</v>
       </c>
       <c r="C14" t="n">
         <v>18589</v>
@@ -103963,7 +103963,7 @@
         <v>64162</v>
       </c>
       <c r="E14" t="n">
-        <v>877734</v>
+        <v>877749</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -103996,7 +103996,7 @@
         <v>24911</v>
       </c>
       <c r="P14" t="n">
-        <v>432426</v>
+        <v>432451</v>
       </c>
       <c r="Q14" t="n">
         <v>36889</v>
@@ -104005,7 +104005,7 @@
         <v>91600</v>
       </c>
       <c r="S14" t="n">
-        <v>2129345</v>
+        <v>2130129</v>
       </c>
     </row>
   </sheetData>
@@ -104697,7 +104697,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>41532</v>
+        <v>41547</v>
       </c>
       <c r="C13" t="n">
         <v>19652</v>
@@ -104721,10 +104721,10 @@
         <v>9059</v>
       </c>
       <c r="J13" t="n">
-        <v>6120</v>
+        <v>6145</v>
       </c>
       <c r="K13" t="n">
-        <v>8621</v>
+        <v>9365</v>
       </c>
       <c r="L13" t="n">
         <v>3575</v>
@@ -104742,7 +104742,7 @@
         <v>27100</v>
       </c>
       <c r="Q13" t="n">
-        <v>213308</v>
+        <v>214092</v>
       </c>
     </row>
     <row r="14">
@@ -104752,7 +104752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>506963</v>
+        <v>506978</v>
       </c>
       <c r="C14" t="n">
         <v>230634</v>
@@ -104776,10 +104776,10 @@
         <v>93618</v>
       </c>
       <c r="J14" t="n">
-        <v>46068</v>
+        <v>46093</v>
       </c>
       <c r="K14" t="n">
-        <v>94683</v>
+        <v>95427</v>
       </c>
       <c r="L14" t="n">
         <v>25543</v>
@@ -104797,7 +104797,7 @@
         <v>325674</v>
       </c>
       <c r="Q14" t="n">
-        <v>2162290</v>
+        <v>2163074</v>
       </c>
     </row>
   </sheetData>
@@ -104852,12 +104852,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -104921,10 +104921,10 @@
         <v>190</v>
       </c>
       <c r="H2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I2" t="n">
         <v>345</v>
-      </c>
-      <c r="I2" t="n">
-        <v>120</v>
       </c>
       <c r="J2" t="n">
         <v>22</v>
@@ -104973,10 +104973,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I3" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
@@ -105025,10 +105025,10 @@
         <v>165</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>410</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -105077,10 +105077,10 @@
         <v>245</v>
       </c>
       <c r="H5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I5" t="n">
         <v>170</v>
-      </c>
-      <c r="I5" t="n">
-        <v>180</v>
       </c>
       <c r="J5" t="n">
         <v>45</v>
@@ -105129,10 +105129,10 @@
         <v>170</v>
       </c>
       <c r="H6" t="n">
+        <v>140</v>
+      </c>
+      <c r="I6" t="n">
         <v>95</v>
-      </c>
-      <c r="I6" t="n">
-        <v>140</v>
       </c>
       <c r="J6" t="n">
         <v>40</v>
@@ -105181,10 +105181,10 @@
         <v>265</v>
       </c>
       <c r="H7" t="n">
+        <v>100</v>
+      </c>
+      <c r="I7" t="n">
         <v>375</v>
-      </c>
-      <c r="I7" t="n">
-        <v>100</v>
       </c>
       <c r="J7" t="n">
         <v>20</v>
@@ -105233,10 +105233,10 @@
         <v>175</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>210</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -105285,10 +105285,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>125</v>
+      </c>
+      <c r="I9" t="n">
         <v>265</v>
-      </c>
-      <c r="I9" t="n">
-        <v>125</v>
       </c>
       <c r="J9" t="n">
         <v>25</v>
@@ -105337,10 +105337,10 @@
         <v>320</v>
       </c>
       <c r="H10" t="n">
+        <v>160</v>
+      </c>
+      <c r="I10" t="n">
         <v>335</v>
-      </c>
-      <c r="I10" t="n">
-        <v>160</v>
       </c>
       <c r="J10" t="n">
         <v>35</v>
@@ -105389,10 +105389,10 @@
         <v>235</v>
       </c>
       <c r="H11" t="n">
+        <v>160</v>
+      </c>
+      <c r="I11" t="n">
         <v>190</v>
-      </c>
-      <c r="I11" t="n">
-        <v>160</v>
       </c>
       <c r="J11" t="n">
         <v>40</v>
@@ -105441,10 +105441,10 @@
         <v>232</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>215</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>90</v>
@@ -105493,10 +105493,10 @@
         <v>105</v>
       </c>
       <c r="H13" t="n">
+        <v>125</v>
+      </c>
+      <c r="I13" t="n">
         <v>297</v>
-      </c>
-      <c r="I13" t="n">
-        <v>125</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -105545,10 +105545,10 @@
         <v>2102</v>
       </c>
       <c r="H14" t="n">
+        <v>1230</v>
+      </c>
+      <c r="I14" t="n">
         <v>2907</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1230</v>
       </c>
       <c r="J14" t="n">
         <v>337</v>
@@ -105624,12 +105624,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -105693,10 +105693,10 @@
         <v>265</v>
       </c>
       <c r="H2" t="n">
+        <v>150</v>
+      </c>
+      <c r="I2" t="n">
         <v>155</v>
-      </c>
-      <c r="I2" t="n">
-        <v>150</v>
       </c>
       <c r="J2" t="n">
         <v>150</v>
@@ -105745,10 +105745,10 @@
         <v>130</v>
       </c>
       <c r="H3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" t="n">
         <v>430</v>
-      </c>
-      <c r="I3" t="n">
-        <v>40</v>
       </c>
       <c r="J3" t="n">
         <v>395</v>
@@ -105797,10 +105797,10 @@
         <v>345</v>
       </c>
       <c r="H4" t="n">
+        <v>160</v>
+      </c>
+      <c r="I4" t="n">
         <v>325</v>
-      </c>
-      <c r="I4" t="n">
-        <v>160</v>
       </c>
       <c r="J4" t="n">
         <v>525</v>
@@ -105849,10 +105849,10 @@
         <v>185</v>
       </c>
       <c r="H5" t="n">
+        <v>580</v>
+      </c>
+      <c r="I5" t="n">
         <v>170</v>
-      </c>
-      <c r="I5" t="n">
-        <v>580</v>
       </c>
       <c r="J5" t="n">
         <v>158</v>
@@ -105901,10 +105901,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>125</v>
+      </c>
+      <c r="I6" t="n">
         <v>335</v>
-      </c>
-      <c r="I6" t="n">
-        <v>125</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -105953,10 +105953,10 @@
         <v>385</v>
       </c>
       <c r="H7" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" t="n">
         <v>125</v>
-      </c>
-      <c r="I7" t="n">
-        <v>300</v>
       </c>
       <c r="J7" t="n">
         <v>325</v>
@@ -106005,10 +106005,10 @@
         <v>385</v>
       </c>
       <c r="H8" t="n">
+        <v>120</v>
+      </c>
+      <c r="I8" t="n">
         <v>325</v>
-      </c>
-      <c r="I8" t="n">
-        <v>120</v>
       </c>
       <c r="J8" t="n">
         <v>70</v>
@@ -106057,10 +106057,10 @@
         <v>520</v>
       </c>
       <c r="H9" t="n">
+        <v>200</v>
+      </c>
+      <c r="I9" t="n">
         <v>225</v>
-      </c>
-      <c r="I9" t="n">
-        <v>200</v>
       </c>
       <c r="J9" t="n">
         <v>165</v>
@@ -106109,10 +106109,10 @@
         <v>735</v>
       </c>
       <c r="H10" t="n">
+        <v>305</v>
+      </c>
+      <c r="I10" t="n">
         <v>285</v>
-      </c>
-      <c r="I10" t="n">
-        <v>305</v>
       </c>
       <c r="J10" t="n">
         <v>387</v>
@@ -106161,10 +106161,10 @@
         <v>415</v>
       </c>
       <c r="H11" t="n">
+        <v>310</v>
+      </c>
+      <c r="I11" t="n">
         <v>490</v>
-      </c>
-      <c r="I11" t="n">
-        <v>310</v>
       </c>
       <c r="J11" t="n">
         <v>101</v>
@@ -106213,10 +106213,10 @@
         <v>400</v>
       </c>
       <c r="H12" t="n">
+        <v>260</v>
+      </c>
+      <c r="I12" t="n">
         <v>355</v>
-      </c>
-      <c r="I12" t="n">
-        <v>260</v>
       </c>
       <c r="J12" t="n">
         <v>80</v>
@@ -106265,10 +106265,10 @@
         <v>250</v>
       </c>
       <c r="H13" t="n">
+        <v>490</v>
+      </c>
+      <c r="I13" t="n">
         <v>289</v>
-      </c>
-      <c r="I13" t="n">
-        <v>490</v>
       </c>
       <c r="J13" t="n">
         <v>75</v>
@@ -106317,10 +106317,10 @@
         <v>4015</v>
       </c>
       <c r="H14" t="n">
+        <v>3040</v>
+      </c>
+      <c r="I14" t="n">
         <v>3509</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3040</v>
       </c>
       <c r="J14" t="n">
         <v>2431</v>
@@ -106396,12 +106396,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Route 7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Route 15</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Route 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -106465,10 +106465,10 @@
         <v>610</v>
       </c>
       <c r="H2" t="n">
+        <v>235</v>
+      </c>
+      <c r="I2" t="n">
         <v>225</v>
-      </c>
-      <c r="I2" t="n">
-        <v>235</v>
       </c>
       <c r="J2" t="n">
         <v>250</v>
@@ -106517,10 +106517,10 @@
         <v>255</v>
       </c>
       <c r="H3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I3" t="n">
         <v>180</v>
-      </c>
-      <c r="I3" t="n">
-        <v>80</v>
       </c>
       <c r="J3" t="n">
         <v>485</v>
@@ -106569,10 +106569,10 @@
         <v>325</v>
       </c>
       <c r="H4" t="n">
+        <v>355</v>
+      </c>
+      <c r="I4" t="n">
         <v>344</v>
-      </c>
-      <c r="I4" t="n">
-        <v>355</v>
       </c>
       <c r="J4" t="n">
         <v>391</v>
@@ -106621,10 +106621,10 @@
         <v>490</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>498</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -106673,10 +106673,10 @@
         <v>400</v>
       </c>
       <c r="H6" t="n">
+        <v>385</v>
+      </c>
+      <c r="I6" t="n">
         <v>398</v>
-      </c>
-      <c r="I6" t="n">
-        <v>385</v>
       </c>
       <c r="J6" t="n">
         <v>448</v>
@@ -106725,10 +106725,10 @@
         <v>425</v>
       </c>
       <c r="H7" t="n">
+        <v>310</v>
+      </c>
+      <c r="I7" t="n">
         <v>823</v>
-      </c>
-      <c r="I7" t="n">
-        <v>310</v>
       </c>
       <c r="J7" t="n">
         <v>120</v>
@@ -106777,10 +106777,10 @@
         <v>650</v>
       </c>
       <c r="H8" t="n">
+        <v>225</v>
+      </c>
+      <c r="I8" t="n">
         <v>158</v>
-      </c>
-      <c r="I8" t="n">
-        <v>225</v>
       </c>
       <c r="J8" t="n">
         <v>120</v>
@@ -106829,10 +106829,10 @@
         <v>335</v>
       </c>
       <c r="H9" t="n">
+        <v>235</v>
+      </c>
+      <c r="I9" t="n">
         <v>631</v>
-      </c>
-      <c r="I9" t="n">
-        <v>235</v>
       </c>
       <c r="J9" t="n">
         <v>100</v>
@@ -106881,10 +106881,10 @@
         <v>525</v>
       </c>
       <c r="H10" t="n">
+        <v>699</v>
+      </c>
+      <c r="I10" t="n">
         <v>515</v>
-      </c>
-      <c r="I10" t="n">
-        <v>699</v>
       </c>
       <c r="J10" t="n">
         <v>405</v>
@@ -106933,10 +106933,10 @@
         <v>130</v>
       </c>
       <c r="H11" t="n">
+        <v>325</v>
+      </c>
+      <c r="I11" t="n">
         <v>274</v>
-      </c>
-      <c r="I11" t="n">
-        <v>325</v>
       </c>
       <c r="J11" t="n">
         <v>40</v>
@@ -106985,10 +106985,10 @@
         <v>895</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>479</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -107037,10 +107037,10 @@
         <v>175</v>
       </c>
       <c r="H13" t="n">
+        <v>375</v>
+      </c>
+      <c r="I13" t="n">
         <v>322</v>
-      </c>
-      <c r="I13" t="n">
-        <v>375</v>
       </c>
       <c r="J13" t="n">
         <v>215</v>
@@ -107089,10 +107089,10 @@
         <v>5215</v>
       </c>
       <c r="H14" t="n">
+        <v>3224</v>
+      </c>
+      <c r="I14" t="n">
         <v>4847</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3224</v>
       </c>
       <c r="J14" t="n">
         <v>2574</v>
